--- a/server/master-excel-files/Kailash_BIOLOGY_Grade 10.xlsx
+++ b/server/master-excel-files/Kailash_BIOLOGY_Grade 10.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\Teachers year plan\ISAP_BIOLOGY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\teacher-year-plan-app\server\master-excel-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="36">
   <si>
     <t>MONTH</t>
   </si>
@@ -82,9 +82,6 @@
   </si>
   <si>
     <t>SECTION-6</t>
-  </si>
-  <si>
-    <t>Completed</t>
   </si>
   <si>
     <t>Revision of Life Processes (Nutrition, Respiration)</t>
@@ -685,11 +682,11 @@
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>6</v>
@@ -718,13 +715,13 @@
         <v>7</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>6</v>
@@ -753,11 +750,11 @@
         <v>9</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>6</v>
@@ -786,13 +783,13 @@
         <v>10</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>6</v>
@@ -821,13 +818,13 @@
         <v>11</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>6</v>
@@ -856,13 +853,13 @@
         <v>12</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>6</v>
@@ -891,13 +888,13 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>6</v>
@@ -926,13 +923,13 @@
         <v>14</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>6</v>
@@ -947,7 +944,7 @@
         <v>6</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>6</v>
@@ -970,9 +967,12 @@
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="E1:K1 E3:G10 J3:K10 H3:I44">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="E1:K1 H11:I42">
       <formula1>"Not Started,In Progress,Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="E3:K10">
+      <formula1>"Not Assigned,In Progress,Completed"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
